--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:13</t>
+    <t xml:space="preserve">2026-09-09 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:07</t>
+    <t xml:space="preserve">2026-09-17 14:03</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:03</t>
+    <t xml:space="preserve">2026-09-23 12:33</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:33</t>
+    <t xml:space="preserve">2026-10-02 13:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_biobio.xlsx
@@ -51,7 +51,7 @@
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">Laja</t>
@@ -99,7 +99,7 @@
     <t xml:space="preserve">Mulchén</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">Santa Juana</t>
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:26</t>
+    <t xml:space="preserve">2026-10-04 08:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_biobio.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_mean_a_2018_biobio.xlsx
@@ -144,7 +144,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:56</t>
+    <t xml:space="preserve">2026-10-05 10:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -852,7 +852,7 @@
         <v>2018</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>221217.12</v>
+        <v>221217.13</v>
       </c>
     </row>
     <row r="19">
